--- a/artfynd/S 3576-2023 artfynd.xlsx
+++ b/artfynd/S 3576-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AZ41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134024</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7111298</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1018,6 +1033,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60485070</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103730008</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1254,6 +1279,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103730032</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1372,6 +1402,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103730066</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1490,6 +1525,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103730083</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1608,6 +1648,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103730112</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1726,6 +1771,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103730165</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1844,6 +1894,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103730182</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1962,6 +2017,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103730194</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2080,6 +2140,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103730214</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2198,6 +2263,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103730229</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2316,6 +2386,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103730239</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2426,6 +2501,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126338364</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2536,6 +2616,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126338442</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2646,6 +2731,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126338464</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2756,6 +2846,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126338481</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2866,6 +2961,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126338496</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2976,6 +3076,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126338520</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3086,6 +3191,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126338534</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3196,6 +3306,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126338555</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3306,6 +3421,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126338576</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3416,6 +3536,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126338613</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3531,6 +3656,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126338687</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3645,6 +3775,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60485202</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3748,6 +3883,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2711870</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3864,6 +4004,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3063312</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3976,6 +4121,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3425388</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4076,6 +4226,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60485073</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4186,6 +4341,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126338449</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4296,6 +4456,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126338468</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4398,6 +4563,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126338482</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4500,6 +4670,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126338749</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4600,6 +4775,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60485080</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4702,6 +4882,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126338768</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4814,6 +4999,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6143862</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4921,6 +5111,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6205421</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5024,6 +5219,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6222869</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5129,8 +5329,55 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6231155</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 3576-2023 artfynd.xlsx
+++ b/artfynd/S 3576-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ41"/>
+  <dimension ref="A1:AZ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3664,10 +3664,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>60485202</v>
+        <v>135690398</v>
       </c>
       <c r="B27" t="n">
-        <v>45046</v>
+        <v>106367</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3675,54 +3675,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102020</v>
+        <v>340</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Smalsprötad bastardsvärmare</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Zygaena osterodensis</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Reiss, 1921</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sandskogen, Svalsjö, Ög</t>
+          <t>Svalsjö, Ög</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>524944</v>
+        <v>524895</v>
       </c>
       <c r="R27" t="n">
         <v>6430593</v>
       </c>
       <c r="S27" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3746,12 +3729,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2016-07-09</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2016-07-09</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3766,68 +3749,79 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Johan Molin</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Johan Molin</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60485202</t>
+          <t>https://artportalen.se/Sighting/135690398</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2711870</v>
+        <v>60485202</v>
       </c>
       <c r="B28" t="n">
-        <v>98186</v>
+        <v>45046</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220250</v>
+        <v>102020</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Smalsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Zygaena osterodensis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>Reiss, 1921</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sandskogen Svalsjö Gata 200 m vä, Ög</t>
+          <t>Sandskogen, Svalsjö, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>524882</v>
+        <v>524944</v>
       </c>
       <c r="R28" t="n">
-        <v>6430571</v>
+        <v>6430593</v>
       </c>
       <c r="S28" t="n">
         <v>100</v>
@@ -3854,12 +3848,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2012-08-07</t>
+          <t>2016-07-09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2012-08-07</t>
+          <t>2016-07-09</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3874,66 +3868,58 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Carin Gondesen</t>
+          <t>Johan Molin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Carin Gondesen</t>
+          <t>Johan Molin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2711870</t>
+          <t>https://artportalen.se/Sighting/60485202</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3063312</v>
+        <v>2711870</v>
       </c>
       <c r="B29" t="n">
-        <v>99118</v>
+        <v>98186</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>220250</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sandskogen Svalsjö Gata 200 m vä, Ög</t>
@@ -3978,11 +3964,6 @@
           <t>2012-08-07</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>17 ex i blom</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4006,41 +3987,45 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3063312</t>
+          <t>https://artportalen.se/Sighting/2711870</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>3425388</v>
+        <v>3063312</v>
       </c>
       <c r="B30" t="n">
-        <v>106244</v>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -4087,12 +4072,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2011-07-10</t>
+          <t>2012-08-07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2011-07-10</t>
+          <t>2012-08-07</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>17 ex i blom</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4103,11 +4093,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>gles tallskog på sandmark</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4123,13 +4108,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3425388</t>
+          <t>https://artportalen.se/Sighting/3063312</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>60485073</v>
+        <v>3425388</v>
       </c>
       <c r="B31" t="n">
         <v>106244</v>
@@ -4158,19 +4143,26 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sandskogen, Svalsjö, Ög</t>
+          <t>Sandskogen Svalsjö Gata 200 m vä, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>524944</v>
+        <v>524882</v>
       </c>
       <c r="R31" t="n">
-        <v>6430593</v>
+        <v>6430571</v>
       </c>
       <c r="S31" t="n">
         <v>100</v>
@@ -4197,12 +4189,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2016-07-09</t>
+          <t>2011-07-10</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2016-07-09</t>
+          <t>2011-07-10</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4213,28 +4205,33 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>gles tallskog på sandmark</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Johan Molin</t>
+          <t>Carin Gondesen</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Johan Molin</t>
+          <t>Carin Gondesen</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60485073</t>
+          <t>https://artportalen.se/Sighting/3425388</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126338449</v>
+        <v>60485073</v>
       </c>
       <c r="B32" t="n">
         <v>106244</v>
@@ -4262,32 +4259,23 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sand, Ög</t>
+          <t>Sandskogen, Svalsjö, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>524943</v>
+        <v>524944</v>
       </c>
       <c r="R32" t="n">
-        <v>6430713</v>
+        <v>6430593</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4311,12 +4299,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2016-07-09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2016-07-09</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4325,31 +4313,30 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Johan Molin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Magnus Wadstein, Claes Svedlindh, Ebba Wadstein</t>
+          <t>Johan Molin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126338449</t>
+          <t>https://artportalen.se/Sighting/60485073</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126338468</v>
+        <v>126338449</v>
       </c>
       <c r="B33" t="n">
         <v>106244</v>
@@ -4396,10 +4383,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>524923</v>
+        <v>524943</v>
       </c>
       <c r="R33" t="n">
-        <v>6430669</v>
+        <v>6430713</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4458,13 +4445,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126338468</t>
+          <t>https://artportalen.se/Sighting/126338449</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126338482</v>
+        <v>126338468</v>
       </c>
       <c r="B34" t="n">
         <v>106244</v>
@@ -4492,8 +4479,16 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
@@ -4503,10 +4498,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>524896</v>
+        <v>524923</v>
       </c>
       <c r="R34" t="n">
-        <v>6430661</v>
+        <v>6430669</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4565,16 +4560,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126338482</t>
+          <t>https://artportalen.se/Sighting/126338468</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126338749</v>
+        <v>126338482</v>
       </c>
       <c r="B35" t="n">
-        <v>97983</v>
+        <v>106244</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4582,21 +4577,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4610,13 +4605,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524930</v>
+        <v>524896</v>
       </c>
       <c r="R35" t="n">
-        <v>6430647</v>
+        <v>6430661</v>
       </c>
       <c r="S35" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4672,16 +4667,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126338749</t>
+          <t>https://artportalen.se/Sighting/126338482</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>60485080</v>
+        <v>126338749</v>
       </c>
       <c r="B36" t="n">
-        <v>97986</v>
+        <v>97983</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4689,16 +4684,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4710,16 +4705,17 @@
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sandskogen, Svalsjö, Ög</t>
+          <t>Sand, Ög</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>524944</v>
+        <v>524930</v>
       </c>
       <c r="R36" t="n">
-        <v>6430593</v>
+        <v>6430647</v>
       </c>
       <c r="S36" t="n">
         <v>100</v>
@@ -4746,12 +4742,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2016-07-09</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2016-07-09</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4760,30 +4756,31 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Johan Molin</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Johan Molin</t>
+          <t>Magnus Wadstein, Claes Svedlindh, Ebba Wadstein</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60485080</t>
+          <t>https://artportalen.se/Sighting/126338749</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126338768</v>
+        <v>60485080</v>
       </c>
       <c r="B37" t="n">
         <v>97986</v>
@@ -4815,17 +4812,16 @@
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sand, Ög</t>
+          <t>Sandskogen, Svalsjö, Ög</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>524930</v>
+        <v>524944</v>
       </c>
       <c r="R37" t="n">
-        <v>6430647</v>
+        <v>6430593</v>
       </c>
       <c r="S37" t="n">
         <v>100</v>
@@ -4852,12 +4848,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2016-07-09</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2016-07-09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4866,79 +4862,72 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Johan Molin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Magnus Wadstein, Claes Svedlindh, Ebba Wadstein</t>
+          <t>Johan Molin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126338768</t>
+          <t>https://artportalen.se/Sighting/60485080</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>6143862</v>
+        <v>126338768</v>
       </c>
       <c r="B38" t="n">
-        <v>106347</v>
+        <v>97986</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>224199</v>
+        <v>221946</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Småsnärjmåra</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Galium spurium subsp. vaillantii</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(DC.) Gaudin</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sandskogen Svalsjö Gata 200 m vä, Ög</t>
+          <t>Sand, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>524882</v>
+        <v>524930</v>
       </c>
       <c r="R38" t="n">
-        <v>6430571</v>
+        <v>6430647</v>
       </c>
       <c r="S38" t="n">
         <v>100</v>
@@ -4965,12 +4954,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2011-07-10</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2011-07-10</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4979,60 +4968,56 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>gles tallskog på sandmark</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Carin Gondesen</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Carin Gondesen</t>
+          <t>Magnus Wadstein, Claes Svedlindh, Ebba Wadstein</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6143862</t>
+          <t>https://artportalen.se/Sighting/126338768</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>6205421</v>
+        <v>6143862</v>
       </c>
       <c r="B39" t="n">
-        <v>97975</v>
+        <v>106347</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>224361</v>
+        <v>224199</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Småsnärjmåra</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Galium spurium subsp. vaillantii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>(DC.) Gaudin</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5041,6 +5026,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sandskogen Svalsjö Gata 200 m vä, Ög</t>
@@ -5096,7 +5086,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>gles  tallskog på sand, mkt mossa</t>
+          <t>gles tallskog på sandmark</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5113,16 +5103,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6205421</t>
+          <t>https://artportalen.se/Sighting/6143862</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>6222869</v>
+        <v>6205421</v>
       </c>
       <c r="B40" t="n">
-        <v>97985</v>
+        <v>97975</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5130,19 +5120,23 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>224363</v>
+        <v>224361</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
@@ -5221,16 +5215,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6222869</t>
+          <t>https://artportalen.se/Sighting/6205421</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>6231155</v>
+        <v>6222869</v>
       </c>
       <c r="B41" t="n">
-        <v>97987</v>
+        <v>97985</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5238,16 +5232,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>224364</v>
+        <v>224363</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
+          <t>Lycopodium annotinum subsp. annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -5257,8 +5251,6 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sandskogen Svalsjö Gata 200 m vä, Ög</t>
@@ -5330,6 +5322,116 @@
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6222869</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>6231155</v>
+      </c>
+      <c r="B42" t="n">
+        <v>97987</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>224364</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Vanlig mattlummer</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Sandskogen Svalsjö Gata 200 m vä, Ög</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>524882</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6430571</v>
+      </c>
+      <c r="S42" t="n">
+        <v>100</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2011-07-10</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2011-07-10</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>gles  tallskog på sand, mkt mossa</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Carin Gondesen</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Carin Gondesen</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/6231155</t>
         </is>
@@ -5377,6 +5479,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 3576-2023 artfynd.xlsx
+++ b/artfynd/S 3576-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ41"/>
+  <dimension ref="A1:AZ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3664,10 +3664,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>60485202</v>
+        <v>135690398</v>
       </c>
       <c r="B27" t="n">
-        <v>45046</v>
+        <v>106372</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3675,54 +3675,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102020</v>
+        <v>340</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Smalsprötad bastardsvärmare</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Zygaena osterodensis</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Reiss, 1921</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sandskogen, Svalsjö, Ög</t>
+          <t>Svalsjö, Ög</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>524944</v>
+        <v>524895</v>
       </c>
       <c r="R27" t="n">
         <v>6430593</v>
       </c>
       <c r="S27" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3746,12 +3729,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2016-07-09</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2016-07-09</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3766,68 +3749,79 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Johan Molin</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Johan Molin</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60485202</t>
+          <t>https://artportalen.se/Sighting/135690398</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2711870</v>
+        <v>60485202</v>
       </c>
       <c r="B28" t="n">
-        <v>98186</v>
+        <v>45046</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220250</v>
+        <v>102020</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Smalsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Zygaena osterodensis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>Reiss, 1921</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sandskogen Svalsjö Gata 200 m vä, Ög</t>
+          <t>Sandskogen, Svalsjö, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>524882</v>
+        <v>524944</v>
       </c>
       <c r="R28" t="n">
-        <v>6430571</v>
+        <v>6430593</v>
       </c>
       <c r="S28" t="n">
         <v>100</v>
@@ -3854,12 +3848,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2012-08-07</t>
+          <t>2016-07-09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2012-08-07</t>
+          <t>2016-07-09</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3874,66 +3868,58 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Carin Gondesen</t>
+          <t>Johan Molin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Carin Gondesen</t>
+          <t>Johan Molin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2711870</t>
+          <t>https://artportalen.se/Sighting/60485202</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3063312</v>
+        <v>2711870</v>
       </c>
       <c r="B29" t="n">
-        <v>99118</v>
+        <v>98186</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>220250</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sandskogen Svalsjö Gata 200 m vä, Ög</t>
@@ -3978,11 +3964,6 @@
           <t>2012-08-07</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>17 ex i blom</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4006,41 +3987,45 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3063312</t>
+          <t>https://artportalen.se/Sighting/2711870</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>3425388</v>
+        <v>3063312</v>
       </c>
       <c r="B30" t="n">
-        <v>106244</v>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -4087,12 +4072,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2011-07-10</t>
+          <t>2012-08-07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2011-07-10</t>
+          <t>2012-08-07</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>17 ex i blom</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4103,11 +4093,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>gles tallskog på sandmark</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4123,13 +4108,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3425388</t>
+          <t>https://artportalen.se/Sighting/3063312</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>60485073</v>
+        <v>3425388</v>
       </c>
       <c r="B31" t="n">
         <v>106244</v>
@@ -4158,19 +4143,26 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sandskogen, Svalsjö, Ög</t>
+          <t>Sandskogen Svalsjö Gata 200 m vä, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>524944</v>
+        <v>524882</v>
       </c>
       <c r="R31" t="n">
-        <v>6430593</v>
+        <v>6430571</v>
       </c>
       <c r="S31" t="n">
         <v>100</v>
@@ -4197,12 +4189,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2016-07-09</t>
+          <t>2011-07-10</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2016-07-09</t>
+          <t>2011-07-10</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4213,28 +4205,33 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>gles tallskog på sandmark</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Johan Molin</t>
+          <t>Carin Gondesen</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Johan Molin</t>
+          <t>Carin Gondesen</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60485073</t>
+          <t>https://artportalen.se/Sighting/3425388</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126338449</v>
+        <v>60485073</v>
       </c>
       <c r="B32" t="n">
         <v>106244</v>
@@ -4262,32 +4259,23 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sand, Ög</t>
+          <t>Sandskogen, Svalsjö, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>524943</v>
+        <v>524944</v>
       </c>
       <c r="R32" t="n">
-        <v>6430713</v>
+        <v>6430593</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4311,12 +4299,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2016-07-09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2016-07-09</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4325,31 +4313,30 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Johan Molin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Magnus Wadstein, Claes Svedlindh, Ebba Wadstein</t>
+          <t>Johan Molin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126338449</t>
+          <t>https://artportalen.se/Sighting/60485073</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126338468</v>
+        <v>126338449</v>
       </c>
       <c r="B33" t="n">
         <v>106244</v>
@@ -4396,10 +4383,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>524923</v>
+        <v>524943</v>
       </c>
       <c r="R33" t="n">
-        <v>6430669</v>
+        <v>6430713</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4458,13 +4445,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126338468</t>
+          <t>https://artportalen.se/Sighting/126338449</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126338482</v>
+        <v>126338468</v>
       </c>
       <c r="B34" t="n">
         <v>106244</v>
@@ -4492,8 +4479,16 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
@@ -4503,10 +4498,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>524896</v>
+        <v>524923</v>
       </c>
       <c r="R34" t="n">
-        <v>6430661</v>
+        <v>6430669</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4565,16 +4560,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126338482</t>
+          <t>https://artportalen.se/Sighting/126338468</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126338749</v>
+        <v>126338482</v>
       </c>
       <c r="B35" t="n">
-        <v>97983</v>
+        <v>106244</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4582,21 +4577,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4610,13 +4605,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524930</v>
+        <v>524896</v>
       </c>
       <c r="R35" t="n">
-        <v>6430647</v>
+        <v>6430661</v>
       </c>
       <c r="S35" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4672,16 +4667,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126338749</t>
+          <t>https://artportalen.se/Sighting/126338482</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>60485080</v>
+        <v>126338749</v>
       </c>
       <c r="B36" t="n">
-        <v>97986</v>
+        <v>97983</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4689,16 +4684,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4710,16 +4705,17 @@
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sandskogen, Svalsjö, Ög</t>
+          <t>Sand, Ög</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>524944</v>
+        <v>524930</v>
       </c>
       <c r="R36" t="n">
-        <v>6430593</v>
+        <v>6430647</v>
       </c>
       <c r="S36" t="n">
         <v>100</v>
@@ -4746,12 +4742,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2016-07-09</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2016-07-09</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4760,30 +4756,31 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Johan Molin</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Johan Molin</t>
+          <t>Magnus Wadstein, Claes Svedlindh, Ebba Wadstein</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60485080</t>
+          <t>https://artportalen.se/Sighting/126338749</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126338768</v>
+        <v>60485080</v>
       </c>
       <c r="B37" t="n">
         <v>97986</v>
@@ -4815,17 +4812,16 @@
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sand, Ög</t>
+          <t>Sandskogen, Svalsjö, Ög</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>524930</v>
+        <v>524944</v>
       </c>
       <c r="R37" t="n">
-        <v>6430647</v>
+        <v>6430593</v>
       </c>
       <c r="S37" t="n">
         <v>100</v>
@@ -4852,12 +4848,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2016-07-09</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2016-07-09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4866,79 +4862,72 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Johan Molin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Magnus Wadstein, Claes Svedlindh, Ebba Wadstein</t>
+          <t>Johan Molin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126338768</t>
+          <t>https://artportalen.se/Sighting/60485080</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>6143862</v>
+        <v>126338768</v>
       </c>
       <c r="B38" t="n">
-        <v>106347</v>
+        <v>97986</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>224199</v>
+        <v>221946</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Småsnärjmåra</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Galium spurium subsp. vaillantii</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(DC.) Gaudin</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sandskogen Svalsjö Gata 200 m vä, Ög</t>
+          <t>Sand, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>524882</v>
+        <v>524930</v>
       </c>
       <c r="R38" t="n">
-        <v>6430571</v>
+        <v>6430647</v>
       </c>
       <c r="S38" t="n">
         <v>100</v>
@@ -4965,12 +4954,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2011-07-10</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2011-07-10</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4979,60 +4968,56 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>gles tallskog på sandmark</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Carin Gondesen</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Carin Gondesen</t>
+          <t>Magnus Wadstein, Claes Svedlindh, Ebba Wadstein</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6143862</t>
+          <t>https://artportalen.se/Sighting/126338768</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>6205421</v>
+        <v>6143862</v>
       </c>
       <c r="B39" t="n">
-        <v>97975</v>
+        <v>106347</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>224361</v>
+        <v>224199</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Småsnärjmåra</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Galium spurium subsp. vaillantii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>(DC.) Gaudin</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5041,6 +5026,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sandskogen Svalsjö Gata 200 m vä, Ög</t>
@@ -5096,7 +5086,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>gles  tallskog på sand, mkt mossa</t>
+          <t>gles tallskog på sandmark</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5113,16 +5103,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6205421</t>
+          <t>https://artportalen.se/Sighting/6143862</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>6222869</v>
+        <v>6205421</v>
       </c>
       <c r="B40" t="n">
-        <v>97985</v>
+        <v>97975</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5130,19 +5120,23 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>224363</v>
+        <v>224361</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
@@ -5221,16 +5215,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6222869</t>
+          <t>https://artportalen.se/Sighting/6205421</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>6231155</v>
+        <v>6222869</v>
       </c>
       <c r="B41" t="n">
-        <v>97987</v>
+        <v>97985</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5238,16 +5232,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>224364</v>
+        <v>224363</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
+          <t>Lycopodium annotinum subsp. annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -5257,8 +5251,6 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sandskogen Svalsjö Gata 200 m vä, Ög</t>
@@ -5330,6 +5322,116 @@
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6222869</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>6231155</v>
+      </c>
+      <c r="B42" t="n">
+        <v>97987</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>224364</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Vanlig mattlummer</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Sandskogen Svalsjö Gata 200 m vä, Ög</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>524882</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6430571</v>
+      </c>
+      <c r="S42" t="n">
+        <v>100</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2011-07-10</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2011-07-10</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>gles  tallskog på sand, mkt mossa</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Carin Gondesen</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Carin Gondesen</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/6231155</t>
         </is>
@@ -5377,6 +5479,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 3576-2023 artfynd.xlsx
+++ b/artfynd/S 3576-2023 artfynd.xlsx
@@ -3667,7 +3667,7 @@
         <v>135690398</v>
       </c>
       <c r="B27" t="n">
-        <v>106372</v>
+        <v>106374</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/S 3576-2023 artfynd.xlsx
+++ b/artfynd/S 3576-2023 artfynd.xlsx
@@ -3667,7 +3667,7 @@
         <v>135690398</v>
       </c>
       <c r="B27" t="n">
-        <v>106374</v>
+        <v>106394</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/S 3576-2023 artfynd.xlsx
+++ b/artfynd/S 3576-2023 artfynd.xlsx
@@ -3667,7 +3667,7 @@
         <v>135690398</v>
       </c>
       <c r="B27" t="n">
-        <v>106394</v>
+        <v>106396</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/S 3576-2023 artfynd.xlsx
+++ b/artfynd/S 3576-2023 artfynd.xlsx
@@ -3667,7 +3667,7 @@
         <v>135690398</v>
       </c>
       <c r="B27" t="n">
-        <v>106396</v>
+        <v>106397</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/S 3576-2023 artfynd.xlsx
+++ b/artfynd/S 3576-2023 artfynd.xlsx
@@ -3667,7 +3667,7 @@
         <v>135690398</v>
       </c>
       <c r="B27" t="n">
-        <v>106397</v>
+        <v>106398</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/S 3576-2023 artfynd.xlsx
+++ b/artfynd/S 3576-2023 artfynd.xlsx
@@ -3667,7 +3667,7 @@
         <v>135690398</v>
       </c>
       <c r="B27" t="n">
-        <v>106398</v>
+        <v>106404</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/S 3576-2023 artfynd.xlsx
+++ b/artfynd/S 3576-2023 artfynd.xlsx
@@ -3667,7 +3667,7 @@
         <v>135690398</v>
       </c>
       <c r="B27" t="n">
-        <v>106404</v>
+        <v>106405</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
